--- a/England 2026/incd_nums.xlsx
+++ b/England 2026/incd_nums.xlsx
@@ -111,61 +111,61 @@
         <v>4.7462238310620304</v>
       </c>
       <c r="I1" s="0">
-        <v>5.3978645428934788</v>
+        <v>5.3978678547071937</v>
       </c>
       <c r="J1" s="0">
-        <v>5.8257351671634403</v>
+        <v>5.8257326020226348</v>
       </c>
       <c r="K1" s="0">
-        <v>5.7078794158767492</v>
+        <v>5.7078783177400538</v>
       </c>
       <c r="L1" s="0">
-        <v>5.7413371784881901</v>
+        <v>5.741336626097441</v>
       </c>
       <c r="M1" s="0">
-        <v>5.7764507374312934</v>
+        <v>5.7764517286055552</v>
       </c>
       <c r="N1" s="0">
-        <v>5.7993545413026633</v>
+        <v>5.7993547643108556</v>
       </c>
       <c r="O1" s="0">
-        <v>5.8127508223759321</v>
+        <v>5.8127481043025933</v>
       </c>
       <c r="P1" s="0">
-        <v>5.8258987435561895</v>
+        <v>5.8258967904600221</v>
       </c>
       <c r="Q1" s="0">
-        <v>5.8392074634550442</v>
+        <v>5.8392062898584527</v>
       </c>
       <c r="R1" s="0">
-        <v>5.8528188495397764</v>
+        <v>5.8528188800921566</v>
       </c>
       <c r="S1" s="0">
-        <v>5.866771198761751</v>
+        <v>5.866770846838409</v>
       </c>
       <c r="T1" s="0">
-        <v>5.8810708107876195</v>
+        <v>5.8810704257544231</v>
       </c>
       <c r="U1" s="0">
-        <v>5.8957150359023469</v>
+        <v>5.8957151389529381</v>
       </c>
       <c r="V1" s="0">
-        <v>5.9106529614116203</v>
+        <v>5.9106529677438653</v>
       </c>
       <c r="W1" s="0">
-        <v>5.9263419025731361</v>
+        <v>5.9263418962123877</v>
       </c>
       <c r="X1" s="0">
-        <v>5.9427044864123539</v>
+        <v>5.9427044706208037</v>
       </c>
       <c r="Y1" s="0">
-        <v>5.9596663682790236</v>
+        <v>5.9596663393799352</v>
       </c>
       <c r="Z1" s="0">
-        <v>5.977158377699852</v>
+        <v>5.9771583879635504</v>
       </c>
       <c r="AA1" s="0">
-        <v>5.995117787251754</v>
+        <v>5.9951178215328707</v>
       </c>
     </row>
     <row r="2">
@@ -194,61 +194,61 @@
         <v>5.2069112833516265</v>
       </c>
       <c r="I2" s="0">
-        <v>5.8936779784096842</v>
+        <v>5.8936823441216832</v>
       </c>
       <c r="J2" s="0">
-        <v>6.3490044644327979</v>
+        <v>6.3489591507253174</v>
       </c>
       <c r="K2" s="0">
-        <v>6.2265116644480925</v>
+        <v>6.2265493920243609</v>
       </c>
       <c r="L2" s="0">
-        <v>6.259310536567523</v>
+        <v>6.2593089237741078</v>
       </c>
       <c r="M2" s="0">
-        <v>6.2954949483083613</v>
+        <v>6.2954940615687436</v>
       </c>
       <c r="N2" s="0">
-        <v>6.3224377530626894</v>
+        <v>6.3224363441595299</v>
       </c>
       <c r="O2" s="0">
-        <v>6.3392546234217209</v>
+        <v>6.3392561782552859</v>
       </c>
       <c r="P2" s="0">
-        <v>6.355794898828635</v>
+        <v>6.355795497672613</v>
       </c>
       <c r="Q2" s="0">
-        <v>6.3724342531238856</v>
+        <v>6.3724346198930562</v>
       </c>
       <c r="R2" s="0">
-        <v>6.3893232556815587</v>
+        <v>6.3893228432155711</v>
       </c>
       <c r="S2" s="0">
-        <v>6.4065111047215435</v>
+        <v>6.4065113489358998</v>
       </c>
       <c r="T2" s="0">
-        <v>6.4240210098343535</v>
+        <v>6.42402105195979</v>
       </c>
       <c r="U2" s="0">
-        <v>6.4418625200183559</v>
+        <v>6.441862422112191</v>
       </c>
       <c r="V2" s="0">
-        <v>6.4599903105865897</v>
+        <v>6.4599903379859613</v>
       </c>
       <c r="W2" s="0">
-        <v>6.478914233044434</v>
+        <v>6.4789142536075897</v>
       </c>
       <c r="X2" s="0">
-        <v>6.4985567948528047</v>
+        <v>6.4985568718426636</v>
       </c>
       <c r="Y2" s="0">
-        <v>6.5188421627950666</v>
+        <v>6.5188422339264864</v>
       </c>
       <c r="Z2" s="0">
-        <v>6.5396986557818107</v>
+        <v>6.5396986999226856</v>
       </c>
       <c r="AA2" s="0">
-        <v>6.5610601517602376</v>
+        <v>6.5610602117204904</v>
       </c>
     </row>
     <row r="3">
@@ -277,1306 +277,1306 @@
         <v>5.4344482801652987</v>
       </c>
       <c r="I3" s="0">
-        <v>6.1411264143769966</v>
+        <v>6.1411277851684538</v>
       </c>
       <c r="J3" s="0">
-        <v>6.6249907917596547</v>
+        <v>6.6249500747259011</v>
       </c>
       <c r="K3" s="0">
-        <v>6.4909533510818314</v>
+        <v>6.4909918375685738</v>
       </c>
       <c r="L3" s="0">
-        <v>6.5191701897660996</v>
+        <v>6.5191707183540766</v>
       </c>
       <c r="M3" s="0">
-        <v>6.5539075296840634</v>
+        <v>6.5539073014004341</v>
       </c>
       <c r="N3" s="0">
-        <v>6.5776491286462679</v>
+        <v>6.5776484740535883</v>
       </c>
       <c r="O3" s="0">
-        <v>6.5917085247211746</v>
+        <v>6.5917094075399616</v>
       </c>
       <c r="P3" s="0">
-        <v>6.6059337449412636</v>
+        <v>6.6059342145761555</v>
       </c>
       <c r="Q3" s="0">
-        <v>6.6205112313444188</v>
+        <v>6.6205114372997249</v>
       </c>
       <c r="R3" s="0">
-        <v>6.6354814216713791</v>
+        <v>6.6354812446710643</v>
       </c>
       <c r="S3" s="0">
-        <v>6.6508282631509328</v>
+        <v>6.650828530953099</v>
       </c>
       <c r="T3" s="0">
-        <v>6.6665378441348526</v>
+        <v>6.6665378985920567</v>
       </c>
       <c r="U3" s="0">
-        <v>6.6826014797442372</v>
+        <v>6.6826015056370904</v>
       </c>
       <c r="V3" s="0">
-        <v>6.6989654418923399</v>
+        <v>6.6989655361760354</v>
       </c>
       <c r="W3" s="0">
-        <v>6.7161584313171341</v>
+        <v>6.7161584924938857</v>
       </c>
       <c r="X3" s="0">
-        <v>6.7341036965660921</v>
+        <v>6.7341038107369515</v>
       </c>
       <c r="Y3" s="0">
-        <v>6.7542336153986371</v>
+        <v>6.7542337296786714</v>
       </c>
       <c r="Z3" s="0">
-        <v>6.7750011027994557</v>
+        <v>6.7750012410316529</v>
       </c>
       <c r="AA3" s="0">
-        <v>6.7963029704085889</v>
+        <v>6.7963030714713986</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>4.5662604994518716</v>
+        <v>5.5015521298241152</v>
       </c>
       <c r="B4" s="0">
-        <v>5.0288468372629112</v>
+        <v>5.120911363747882</v>
       </c>
       <c r="C4" s="0">
-        <v>5.2841745584848256</v>
+        <v>4.7675943510544787</v>
       </c>
       <c r="D4" s="0">
-        <v>4.8429759674198296</v>
+        <v>4.5662605147835809</v>
       </c>
       <c r="E4" s="0">
-        <v>4.7897035556538725</v>
+        <v>4.5075868683203471</v>
       </c>
       <c r="F4" s="0">
-        <v>4.7167236006779261</v>
+        <v>4.4309514886866639</v>
       </c>
       <c r="G4" s="0">
-        <v>4.674838450921543</v>
+        <v>4.3896133393880765</v>
       </c>
       <c r="H4" s="0">
-        <v>4.9956514726037495</v>
+        <v>4.7462238310620304</v>
       </c>
       <c r="I4" s="0">
-        <v>5.6009457119042123</v>
+        <v>5.3978678547071937</v>
       </c>
       <c r="J4" s="0">
-        <v>6.0530331248341414</v>
+        <v>5.8257326020226348</v>
       </c>
       <c r="K4" s="0">
-        <v>6.0310245014807631</v>
+        <v>5.7078783177400538</v>
       </c>
       <c r="L4" s="0">
-        <v>6.0777639652529718</v>
+        <v>5.741336626097441</v>
       </c>
       <c r="M4" s="0">
-        <v>6.1188758986763867</v>
+        <v>5.7764520130337891</v>
       </c>
       <c r="N4" s="0">
-        <v>6.139791610793913</v>
+        <v>5.7908300947394968</v>
       </c>
       <c r="O4" s="0">
-        <v>6.1124897940072103</v>
+        <v>5.7596231303053385</v>
       </c>
       <c r="P4" s="0">
-        <v>6.0483161987403289</v>
+        <v>5.6945710120148876</v>
       </c>
       <c r="Q4" s="0">
-        <v>5.9582421584545244</v>
+        <v>5.605786190087187</v>
       </c>
       <c r="R4" s="0">
-        <v>5.8512468857776669</v>
+        <v>5.5026881479642924</v>
       </c>
       <c r="S4" s="0">
-        <v>5.735575836141221</v>
+        <v>5.3932612118401764</v>
       </c>
       <c r="T4" s="0">
-        <v>5.6196517161639568</v>
+        <v>5.2836505991563385</v>
       </c>
       <c r="U4" s="0">
-        <v>5.5077767771168507</v>
+        <v>5.1780908976972553</v>
       </c>
       <c r="V4" s="0">
-        <v>5.402458658245223</v>
+        <v>5.0836504923966004</v>
       </c>
       <c r="W4" s="0">
-        <v>5.3181791535576855</v>
+        <v>5.0131385344093831</v>
       </c>
       <c r="X4" s="0">
-        <v>5.256243267196699</v>
+        <v>4.9611968988914406</v>
       </c>
       <c r="Y4" s="0">
-        <v>5.2096997949999793</v>
+        <v>4.9223640828537718</v>
       </c>
       <c r="Z4" s="0">
-        <v>5.174227280143211</v>
+        <v>4.8930893897510979</v>
       </c>
       <c r="AA4" s="0">
-        <v>5.147001273385845</v>
+        <v>4.8709557308149485</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>4.5075868531063179</v>
+        <v>6.0255604383483581</v>
       </c>
       <c r="B5" s="0">
-        <v>4.9678254851893779</v>
+        <v>5.6210581029032545</v>
       </c>
       <c r="C5" s="0">
-        <v>5.2095146913776844</v>
+        <v>5.2434607810681069</v>
       </c>
       <c r="D5" s="0">
-        <v>5.0640192241538049</v>
+        <v>5.0288468426608635</v>
       </c>
       <c r="E5" s="0">
-        <v>4.9972234804941511</v>
+        <v>4.9678254906186146</v>
       </c>
       <c r="F5" s="0">
-        <v>4.9205079121903754</v>
+        <v>4.8834007922916465</v>
       </c>
       <c r="G5" s="0">
-        <v>4.8706492803499213</v>
+        <v>4.8314440871030193</v>
       </c>
       <c r="H5" s="0">
-        <v>5.1725532234726472</v>
+        <v>5.2069112833516265</v>
       </c>
       <c r="I5" s="0">
-        <v>5.7726478499706966</v>
+        <v>5.8936823441216832</v>
       </c>
       <c r="J5" s="0">
-        <v>6.230562389220129</v>
+        <v>6.3489591507253174</v>
       </c>
       <c r="K5" s="0">
-        <v>6.1814624299680903</v>
+        <v>6.2265493920243609</v>
       </c>
       <c r="L5" s="0">
-        <v>6.2054344228358875</v>
+        <v>6.2593089237741078</v>
       </c>
       <c r="M5" s="0">
-        <v>6.2322405892496633</v>
+        <v>6.2954942131585483</v>
       </c>
       <c r="N5" s="0">
-        <v>6.245157589884041</v>
+        <v>6.3127053665461279</v>
       </c>
       <c r="O5" s="0">
-        <v>6.2089707407183887</v>
+        <v>6.2783692176589101</v>
       </c>
       <c r="P5" s="0">
-        <v>6.1422965787615338</v>
+        <v>6.2051442962457877</v>
       </c>
       <c r="Q5" s="0">
-        <v>6.0554736074726581</v>
+        <v>6.1047042455460767</v>
       </c>
       <c r="R5" s="0">
-        <v>5.9610893708303037</v>
+        <v>5.987856979933107</v>
       </c>
       <c r="S5" s="0">
-        <v>5.8595238298190333</v>
+        <v>5.8647737335292982</v>
       </c>
       <c r="T5" s="0">
-        <v>5.7390039521252332</v>
+        <v>5.7422928671531706</v>
       </c>
       <c r="U5" s="0">
-        <v>5.6308292040515164</v>
+        <v>5.6238936340411643</v>
       </c>
       <c r="V5" s="0">
-        <v>5.5371384944074986</v>
+        <v>5.5173005116956633</v>
       </c>
       <c r="W5" s="0">
-        <v>5.4666826224540044</v>
+        <v>5.4366261982755208</v>
       </c>
       <c r="X5" s="0">
-        <v>5.4062196068862267</v>
+        <v>5.3760692709168243</v>
       </c>
       <c r="Y5" s="0">
-        <v>5.3595146439962154</v>
+        <v>5.3296567238587791</v>
       </c>
       <c r="Z5" s="0">
-        <v>5.3231050150124481</v>
+        <v>5.2935876250863139</v>
       </c>
       <c r="AA5" s="0">
-        <v>5.2945172655486266</v>
+        <v>5.265542839888683</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>4.4309533321409074</v>
+        <v>6.3459701660162464</v>
       </c>
       <c r="B6" s="0">
-        <v>4.8834008180834072</v>
+        <v>5.9165705033746949</v>
       </c>
       <c r="C6" s="0">
-        <v>5.1126299349761606</v>
+        <v>5.5163494122852672</v>
       </c>
       <c r="D6" s="0">
-        <v>5.1956602407528756</v>
+        <v>5.2841746591402865</v>
       </c>
       <c r="E6" s="0">
-        <v>5.1444170639299589</v>
+        <v>5.2095147652677305</v>
       </c>
       <c r="F6" s="0">
-        <v>5.0708546946197677</v>
+        <v>5.1126321085863315</v>
       </c>
       <c r="G6" s="0">
-        <v>5.0258593702801422</v>
+        <v>5.0567691173318199</v>
       </c>
       <c r="H6" s="0">
-        <v>5.3145699738519063</v>
+        <v>5.4344482801652987</v>
       </c>
       <c r="I6" s="0">
-        <v>5.9935835918551863</v>
+        <v>6.1411277851684538</v>
       </c>
       <c r="J6" s="0">
-        <v>6.5155305808313191</v>
+        <v>6.6249500747259011</v>
       </c>
       <c r="K6" s="0">
-        <v>6.5023256571086199</v>
+        <v>6.4909918375685738</v>
       </c>
       <c r="L6" s="0">
-        <v>6.5523309305108937</v>
+        <v>6.5191707183540766</v>
       </c>
       <c r="M6" s="0">
-        <v>6.5971513899120549</v>
+        <v>6.5539075701525462</v>
       </c>
       <c r="N6" s="0">
-        <v>6.6197552618023758</v>
+        <v>6.5671849250149918</v>
       </c>
       <c r="O6" s="0">
-        <v>6.5870771043822227</v>
+        <v>6.5262056073779995</v>
       </c>
       <c r="P6" s="0">
-        <v>6.5116274412108561</v>
+        <v>6.4442524300195343</v>
       </c>
       <c r="Q6" s="0">
-        <v>6.4063571455906905</v>
+        <v>6.3341193375555491</v>
       </c>
       <c r="R6" s="0">
-        <v>6.2831186089601685</v>
+        <v>6.2139756385688107</v>
       </c>
       <c r="S6" s="0">
-        <v>6.1517838883657081</v>
+        <v>6.0910809456717043</v>
       </c>
       <c r="T6" s="0">
-        <v>6.0198254404407292</v>
+        <v>5.9676842002745367</v>
       </c>
       <c r="U6" s="0">
-        <v>5.8923822146049103</v>
+        <v>5.8483260601246023</v>
       </c>
       <c r="V6" s="0">
-        <v>5.7777299588487834</v>
+        <v>5.7407934380074037</v>
       </c>
       <c r="W6" s="0">
-        <v>5.691885222145177</v>
+        <v>5.6595446819930144</v>
       </c>
       <c r="X6" s="0">
-        <v>5.6291333430554493</v>
+        <v>5.5987297943026535</v>
       </c>
       <c r="Y6" s="0">
-        <v>5.5822824963449413</v>
+        <v>5.5522145098297262</v>
       </c>
       <c r="Z6" s="0">
-        <v>5.5469208860792838</v>
+        <v>5.5161057290282818</v>
       </c>
       <c r="AA6" s="0">
-        <v>5.5201313927718774</v>
+        <v>5.4878256489842405</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>4.3896133078557078</v>
+        <v>5.5015521298241152</v>
       </c>
       <c r="B7" s="0">
-        <v>4.8314441524448206</v>
+        <v>5.120911363747882</v>
       </c>
       <c r="C7" s="0">
-        <v>5.0567706854733219</v>
+        <v>4.7675943510544787</v>
       </c>
       <c r="D7" s="0">
-        <v>4.8429759674198296</v>
+        <v>4.5662605147835809</v>
       </c>
       <c r="E7" s="0">
-        <v>4.7897035556538725</v>
+        <v>4.5075868683203471</v>
       </c>
       <c r="F7" s="0">
-        <v>4.7167236006779261</v>
+        <v>4.4309514886866639</v>
       </c>
       <c r="G7" s="0">
-        <v>4.674838450921543</v>
+        <v>4.3896133393880765</v>
       </c>
       <c r="H7" s="0">
-        <v>4.9956514726037495</v>
+        <v>4.7462238310620304</v>
       </c>
       <c r="I7" s="0">
-        <v>5.6009457119042123</v>
+        <v>5.3978678547071937</v>
       </c>
       <c r="J7" s="0">
-        <v>6.0530331248341414</v>
+        <v>5.8257326020226348</v>
       </c>
       <c r="K7" s="0">
-        <v>6.0310245014807631</v>
+        <v>5.7078783177400538</v>
       </c>
       <c r="L7" s="0">
-        <v>6.0777639652529718</v>
+        <v>5.741336626097441</v>
       </c>
       <c r="M7" s="0">
-        <v>6.1188758986545233</v>
+        <v>5.7764520129644916</v>
       </c>
       <c r="N7" s="0">
-        <v>6.1396789798459262</v>
+        <v>5.7907207498066295</v>
       </c>
       <c r="O7" s="0">
-        <v>6.1120174856682814</v>
+        <v>5.7591618749462095</v>
       </c>
       <c r="P7" s="0">
-        <v>6.047506914555755</v>
+        <v>5.6937842855273786</v>
       </c>
       <c r="Q7" s="0">
-        <v>5.9571718715806758</v>
+        <v>5.6047577059656764</v>
       </c>
       <c r="R7" s="0">
-        <v>5.8503396256630991</v>
+        <v>5.5014988170047365</v>
       </c>
       <c r="S7" s="0">
-        <v>5.7345966185989905</v>
+        <v>5.3919843409394019</v>
       </c>
       <c r="T7" s="0">
-        <v>5.618648608597578</v>
+        <v>5.2823520795077279</v>
       </c>
       <c r="U7" s="0">
-        <v>5.5067984835855626</v>
+        <v>5.1768296160634177</v>
       </c>
       <c r="V7" s="0">
-        <v>5.401502468587946</v>
+        <v>5.0825924181456346</v>
       </c>
       <c r="W7" s="0">
-        <v>5.3176484998563254</v>
+        <v>5.0125831056745946</v>
       </c>
       <c r="X7" s="0">
-        <v>5.2561427744514475</v>
+        <v>4.9611486219565775</v>
       </c>
       <c r="Y7" s="0">
-        <v>5.209976670966415</v>
+        <v>4.9227610262020098</v>
       </c>
       <c r="Z7" s="0">
-        <v>5.1748342310006379</v>
+        <v>4.8938757931432191</v>
       </c>
       <c r="AA7" s="0">
-        <v>5.1479018950631357</v>
+        <v>4.8720882691664773</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>4.7462232678497447</v>
+        <v>6.0255604383483581</v>
       </c>
       <c r="B8" s="0">
-        <v>5.2069130221445628</v>
+        <v>5.6210581029032545</v>
       </c>
       <c r="C8" s="0">
-        <v>5.4344496582197364</v>
+        <v>5.2434607810681069</v>
       </c>
       <c r="D8" s="0">
-        <v>5.0640192241538049</v>
+        <v>5.0288468426608635</v>
       </c>
       <c r="E8" s="0">
-        <v>4.9972234804941511</v>
+        <v>4.9678254906186146</v>
       </c>
       <c r="F8" s="0">
-        <v>4.9205079121903754</v>
+        <v>4.8834007922916465</v>
       </c>
       <c r="G8" s="0">
-        <v>4.8706492803499213</v>
+        <v>4.8314440871030193</v>
       </c>
       <c r="H8" s="0">
-        <v>5.1725532234726472</v>
+        <v>5.2069112833516265</v>
       </c>
       <c r="I8" s="0">
-        <v>5.7726478499706966</v>
+        <v>5.8936823441216832</v>
       </c>
       <c r="J8" s="0">
-        <v>6.230562389220129</v>
+        <v>6.3489591507253174</v>
       </c>
       <c r="K8" s="0">
-        <v>6.1814624299680903</v>
+        <v>6.2265493920243609</v>
       </c>
       <c r="L8" s="0">
-        <v>6.2054344228358875</v>
+        <v>6.2593089237741078</v>
       </c>
       <c r="M8" s="0">
-        <v>6.2322405892282209</v>
+        <v>6.2954942131365064</v>
       </c>
       <c r="N8" s="0">
-        <v>6.2450635916409816</v>
+        <v>6.3125988749284891</v>
       </c>
       <c r="O8" s="0">
-        <v>6.2087652198263497</v>
+        <v>6.2779189142799847</v>
       </c>
       <c r="P8" s="0">
-        <v>6.1419476698108673</v>
+        <v>6.2043746234108559</v>
       </c>
       <c r="Q8" s="0">
-        <v>6.0545117019339108</v>
+        <v>6.1036950988827607</v>
       </c>
       <c r="R8" s="0">
-        <v>5.9599685774120195</v>
+        <v>5.9866856354708835</v>
       </c>
       <c r="S8" s="0">
-        <v>5.8583095836179169</v>
+        <v>5.8636098937939556</v>
       </c>
       <c r="T8" s="0">
-        <v>5.7379600182168033</v>
+        <v>5.7411006919708472</v>
       </c>
       <c r="U8" s="0">
-        <v>5.6302550264993085</v>
+        <v>5.6227249487741409</v>
       </c>
       <c r="V8" s="0">
-        <v>5.5366465628144859</v>
+        <v>5.5163046167397392</v>
       </c>
       <c r="W8" s="0">
-        <v>5.4663457960773423</v>
+        <v>5.4360737845000653</v>
       </c>
       <c r="X8" s="0">
-        <v>5.4060699201749323</v>
+        <v>5.3759655164920455</v>
       </c>
       <c r="Y8" s="0">
-        <v>5.3597637429306957</v>
+        <v>5.3299475810396473</v>
       </c>
       <c r="Z8" s="0">
-        <v>5.3237072430877728</v>
+        <v>5.2942250275806968</v>
       </c>
       <c r="AA8" s="0">
-        <v>5.295437180163943</v>
+        <v>5.266554776482077</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>5.397866381944219</v>
+        <v>6.3459701660162464</v>
       </c>
       <c r="B9" s="0">
-        <v>5.8936782230152574</v>
+        <v>5.9165705033746949</v>
       </c>
       <c r="C9" s="0">
-        <v>6.1411254595300058</v>
+        <v>5.5163494122852672</v>
       </c>
       <c r="D9" s="0">
-        <v>5.1956602407528756</v>
+        <v>5.2841746591402865</v>
       </c>
       <c r="E9" s="0">
-        <v>5.1444170639299589</v>
+        <v>5.2095147652677305</v>
       </c>
       <c r="F9" s="0">
-        <v>5.0708546946197677</v>
+        <v>5.1126321085863315</v>
       </c>
       <c r="G9" s="0">
-        <v>5.0258593702801422</v>
+        <v>5.0567691173318199</v>
       </c>
       <c r="H9" s="0">
-        <v>5.3145699738519063</v>
+        <v>5.4344482801652987</v>
       </c>
       <c r="I9" s="0">
-        <v>5.9935835918551863</v>
+        <v>6.1411277851684538</v>
       </c>
       <c r="J9" s="0">
-        <v>6.5155305808313191</v>
+        <v>6.6249500747259011</v>
       </c>
       <c r="K9" s="0">
-        <v>6.5023256571086199</v>
+        <v>6.4909918375685738</v>
       </c>
       <c r="L9" s="0">
-        <v>6.5523309305108937</v>
+        <v>6.5191707183540766</v>
       </c>
       <c r="M9" s="0">
-        <v>6.5971513899112342</v>
+        <v>6.5539075699510212</v>
       </c>
       <c r="N9" s="0">
-        <v>6.6196477285446669</v>
+        <v>6.5671033156383256</v>
       </c>
       <c r="O9" s="0">
-        <v>6.5866204105039037</v>
+        <v>6.5258614526886936</v>
       </c>
       <c r="P9" s="0">
-        <v>6.5108432361516488</v>
+        <v>6.4436659169845569</v>
       </c>
       <c r="Q9" s="0">
-        <v>6.4053246472891861</v>
+        <v>6.3333543697362087</v>
       </c>
       <c r="R9" s="0">
-        <v>6.2819158315171686</v>
+        <v>6.2129113162415726</v>
       </c>
       <c r="S9" s="0">
-        <v>6.1504822991444623</v>
+        <v>6.0899229650103592</v>
       </c>
       <c r="T9" s="0">
-        <v>6.0184899155297158</v>
+        <v>5.96649630472435</v>
       </c>
       <c r="U9" s="0">
-        <v>5.8910673511244198</v>
+        <v>5.8471587992997076</v>
       </c>
       <c r="V9" s="0">
-        <v>5.7766055949502473</v>
+        <v>5.7397944597382455</v>
       </c>
       <c r="W9" s="0">
-        <v>5.691257494456754</v>
+        <v>5.6589828191037927</v>
       </c>
       <c r="X9" s="0">
-        <v>5.6290002416661329</v>
+        <v>5.5986095673181362</v>
       </c>
       <c r="Y9" s="0">
-        <v>5.582584909895993</v>
+        <v>5.5524815905688847</v>
       </c>
       <c r="Z9" s="0">
-        <v>5.5476049447094233</v>
+        <v>5.516711871438325</v>
       </c>
       <c r="AA9" s="0">
-        <v>5.5211551425277117</v>
+        <v>5.4887339011113925</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>5.8257358994860091</v>
+        <v>5.5015521298241152</v>
       </c>
       <c r="B10" s="0">
-        <v>6.3490046559259428</v>
+        <v>5.120911363747882</v>
       </c>
       <c r="C10" s="0">
-        <v>6.6249908164213434</v>
+        <v>4.7675943510544787</v>
       </c>
       <c r="D10" s="0">
-        <v>4.8429759674198296</v>
+        <v>4.5662605147835809</v>
       </c>
       <c r="E10" s="0">
-        <v>4.7897035556538725</v>
+        <v>4.5075868683203471</v>
       </c>
       <c r="F10" s="0">
-        <v>4.7167236006779261</v>
+        <v>4.4309514886866639</v>
       </c>
       <c r="G10" s="0">
-        <v>4.674838450921543</v>
+        <v>4.3896133393880765</v>
       </c>
       <c r="H10" s="0">
-        <v>4.9956514726037495</v>
+        <v>4.7462238310620304</v>
       </c>
       <c r="I10" s="0">
-        <v>5.6009457119042123</v>
+        <v>5.3978678547071937</v>
       </c>
       <c r="J10" s="0">
-        <v>6.0530331248341414</v>
+        <v>5.8257326020226348</v>
       </c>
       <c r="K10" s="0">
-        <v>6.0310245014807631</v>
+        <v>5.7078783177400538</v>
       </c>
       <c r="L10" s="0">
-        <v>6.0777639652529718</v>
+        <v>5.741336626097441</v>
       </c>
       <c r="M10" s="0">
-        <v>6.1188758986201259</v>
+        <v>5.7764520129482726</v>
       </c>
       <c r="N10" s="0">
-        <v>6.1376577273617423</v>
+        <v>5.7892636058913825</v>
       </c>
       <c r="O10" s="0">
-        <v>6.0903152808743508</v>
+        <v>5.7425285383942937</v>
       </c>
       <c r="P10" s="0">
-        <v>5.9776677473844417</v>
+        <v>5.6379779058020558</v>
       </c>
       <c r="Q10" s="0">
-        <v>5.8061570214429459</v>
+        <v>5.4875904495380086</v>
       </c>
       <c r="R10" s="0">
-        <v>5.5942018389025705</v>
+        <v>5.307648606739872</v>
       </c>
       <c r="S10" s="0">
-        <v>5.3599310952117785</v>
+        <v>5.1137558851310043</v>
       </c>
       <c r="T10" s="0">
-        <v>5.1189166413256855</v>
+        <v>4.9186055008707878</v>
       </c>
       <c r="U10" s="0">
-        <v>4.8840424934004769</v>
+        <v>4.7312735952549403</v>
       </c>
       <c r="V10" s="0">
-        <v>4.6690523465627685</v>
+        <v>4.5627437491439675</v>
       </c>
       <c r="W10" s="0">
-        <v>4.4969478252568171</v>
+        <v>4.4329284096523143</v>
       </c>
       <c r="X10" s="0">
-        <v>4.3667831183912496</v>
+        <v>4.3392324501951114</v>
       </c>
       <c r="Y10" s="0">
-        <v>4.2702570781462566</v>
+        <v>4.2730830778188311</v>
       </c>
       <c r="Z10" s="0">
-        <v>4.1994505941057616</v>
+        <v>4.2268005772151236</v>
       </c>
       <c r="AA10" s="0">
-        <v>4.1477296234765779</v>
+        <v>4.1945448344016887</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>5.7078803888894161</v>
+        <v>6.0255604383483581</v>
       </c>
       <c r="B11" s="0">
-        <v>6.2265118269087179</v>
+        <v>5.6210581029032545</v>
       </c>
       <c r="C11" s="0">
-        <v>6.4909524348818879</v>
+        <v>5.2434607810681069</v>
       </c>
       <c r="D11" s="0">
-        <v>5.0640192241538049</v>
+        <v>5.0288468426608635</v>
       </c>
       <c r="E11" s="0">
-        <v>4.9972234804941511</v>
+        <v>4.9678254906186146</v>
       </c>
       <c r="F11" s="0">
-        <v>4.9205079121903754</v>
+        <v>4.8834007922916465</v>
       </c>
       <c r="G11" s="0">
-        <v>4.8706492803499213</v>
+        <v>4.8314440871030193</v>
       </c>
       <c r="H11" s="0">
-        <v>5.1725532234726472</v>
+        <v>5.2069112833516265</v>
       </c>
       <c r="I11" s="0">
-        <v>5.7726478499706966</v>
+        <v>5.8936823441216832</v>
       </c>
       <c r="J11" s="0">
-        <v>6.230562389220129</v>
+        <v>6.3489591507253174</v>
       </c>
       <c r="K11" s="0">
-        <v>6.1814624299680903</v>
+        <v>6.2265493920243609</v>
       </c>
       <c r="L11" s="0">
-        <v>6.2054344228358875</v>
+        <v>6.2593089237741078</v>
       </c>
       <c r="M11" s="0">
-        <v>6.2322405891960582</v>
+        <v>6.2954942131365064</v>
       </c>
       <c r="N11" s="0">
-        <v>6.2429532798318688</v>
+        <v>6.3107317297612182</v>
       </c>
       <c r="O11" s="0">
-        <v>6.1871744215952837</v>
+        <v>6.2573259915853479</v>
       </c>
       <c r="P11" s="0">
-        <v>6.0670615594769952</v>
+        <v>6.1362681338484011</v>
       </c>
       <c r="Q11" s="0">
-        <v>5.8898289961531312</v>
+        <v>5.9614838013652616</v>
       </c>
       <c r="R11" s="0">
-        <v>5.6838650214674544</v>
+        <v>5.7518503256117297</v>
       </c>
       <c r="S11" s="0">
-        <v>5.4544913991939863</v>
+        <v>5.5255410210444795</v>
       </c>
       <c r="T11" s="0">
-        <v>5.2249929958690871</v>
+        <v>5.2974672894988508</v>
       </c>
       <c r="U11" s="0">
-        <v>4.9973997308371612</v>
+        <v>5.0783927928954</v>
       </c>
       <c r="V11" s="0">
-        <v>4.809739512128882</v>
+        <v>4.881207812038407</v>
       </c>
       <c r="W11" s="0">
-        <v>4.6356750850732338</v>
+        <v>4.7271330137726419</v>
       </c>
       <c r="X11" s="0">
-        <v>4.5072087316212182</v>
+        <v>4.6077345578675084</v>
       </c>
       <c r="Y11" s="0">
-        <v>4.4140803930299883</v>
+        <v>4.53578337472557</v>
       </c>
       <c r="Z11" s="0">
-        <v>4.356790547243091</v>
+        <v>4.4850757583792742</v>
       </c>
       <c r="AA11" s="0">
-        <v>4.3183227611824915</v>
+        <v>4.4484952491278644</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>5.7413378339774628</v>
+        <v>6.3459701660162464</v>
       </c>
       <c r="B12" s="0">
-        <v>6.2593106718806126</v>
+        <v>5.9165705033746949</v>
       </c>
       <c r="C12" s="0">
-        <v>6.5191693463607035</v>
+        <v>5.5163494122852672</v>
       </c>
       <c r="D12" s="0">
-        <v>5.1956602407528756</v>
+        <v>5.2841746591402865</v>
       </c>
       <c r="E12" s="0">
-        <v>5.1444170639299589</v>
+        <v>5.2095147652677305</v>
       </c>
       <c r="F12" s="0">
-        <v>5.0708546946197677</v>
+        <v>5.1126321085863315</v>
       </c>
       <c r="G12" s="0">
-        <v>5.0258593702801422</v>
+        <v>5.0567691173318199</v>
       </c>
       <c r="H12" s="0">
-        <v>5.3145699738519063</v>
+        <v>5.4344482801652987</v>
       </c>
       <c r="I12" s="0">
-        <v>5.9935835918551863</v>
+        <v>6.1411277851684538</v>
       </c>
       <c r="J12" s="0">
-        <v>6.5155305808313191</v>
+        <v>6.6249500747259011</v>
       </c>
       <c r="K12" s="0">
-        <v>6.5023256571086199</v>
+        <v>6.4909918375685738</v>
       </c>
       <c r="L12" s="0">
-        <v>6.5523309305108937</v>
+        <v>6.5191707183540766</v>
       </c>
       <c r="M12" s="0">
-        <v>6.5971513899109597</v>
+        <v>6.5539075697071771</v>
       </c>
       <c r="N12" s="0">
-        <v>6.6171647419168576</v>
+        <v>6.5653109451211549</v>
       </c>
       <c r="O12" s="0">
-        <v>6.560530035047206</v>
+        <v>6.5054435543268836</v>
       </c>
       <c r="P12" s="0">
-        <v>6.4273161593638326</v>
+        <v>6.3737807904252248</v>
       </c>
       <c r="Q12" s="0">
-        <v>6.2345001024856766</v>
+        <v>6.1833137037860375</v>
       </c>
       <c r="R12" s="0">
-        <v>6.0035729476328879</v>
+        <v>5.960658500878286</v>
       </c>
       <c r="S12" s="0">
-        <v>5.7547295140783667</v>
+        <v>5.7237931054930957</v>
       </c>
       <c r="T12" s="0">
-        <v>5.5043743424875426</v>
+        <v>5.4850215683822681</v>
       </c>
       <c r="U12" s="0">
-        <v>5.2642854649741029</v>
+        <v>5.2555903678311857</v>
       </c>
       <c r="V12" s="0">
-        <v>5.0483362604699833</v>
+        <v>5.0489234537381487</v>
       </c>
       <c r="W12" s="0">
-        <v>4.8828234107935637</v>
+        <v>4.8892415803034552</v>
       </c>
       <c r="X12" s="0">
-        <v>4.7644068356497984</v>
+        <v>4.7736315590145191</v>
       </c>
       <c r="Y12" s="0">
-        <v>4.6810520147556547</v>
+        <v>4.6915209866969123</v>
       </c>
       <c r="Z12" s="0">
-        <v>4.6227898800501128</v>
+        <v>4.635004815139796</v>
       </c>
       <c r="AA12" s="0">
-        <v>4.5822754578282741</v>
+        <v>4.5963203143826279</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>5.7764506124248305</v>
+        <v>5.5015521298241152</v>
       </c>
       <c r="B13" s="0">
-        <v>6.2954951023993928</v>
+        <v>5.120911363747882</v>
       </c>
       <c r="C13" s="0">
-        <v>6.5539067801699273</v>
+        <v>4.7675943510544787</v>
       </c>
       <c r="D13" s="0">
-        <v>4.8429759674198296</v>
+        <v>4.5662605147835809</v>
       </c>
       <c r="E13" s="0">
-        <v>4.7897035556538725</v>
+        <v>4.5075868683203471</v>
       </c>
       <c r="F13" s="0">
-        <v>4.7167236006779261</v>
+        <v>4.4309514886866639</v>
       </c>
       <c r="G13" s="0">
-        <v>4.674838450921543</v>
+        <v>4.3896133393880765</v>
       </c>
       <c r="H13" s="0">
-        <v>4.9956514726037495</v>
+        <v>4.7462238310620304</v>
       </c>
       <c r="I13" s="0">
-        <v>5.6009457119042123</v>
+        <v>5.3978678547071937</v>
       </c>
       <c r="J13" s="0">
-        <v>6.0530331248341414</v>
+        <v>5.8257326020226348</v>
       </c>
       <c r="K13" s="0">
-        <v>6.0310245014807631</v>
+        <v>5.7078783177400538</v>
       </c>
       <c r="L13" s="0">
-        <v>6.0777639652529718</v>
+        <v>5.741336626097441</v>
       </c>
       <c r="M13" s="0">
-        <v>6.1188758986203933</v>
+        <v>5.7764520129480035</v>
       </c>
       <c r="N13" s="0">
-        <v>6.1375763092726476</v>
+        <v>5.7892445941336579</v>
       </c>
       <c r="O13" s="0">
-        <v>6.0889412630254025</v>
+        <v>5.7417957374610413</v>
       </c>
       <c r="P13" s="0">
-        <v>5.9719893626784222</v>
+        <v>5.6342772988509546</v>
       </c>
       <c r="Q13" s="0">
-        <v>5.7964945858191834</v>
+        <v>5.4781012291360209</v>
       </c>
       <c r="R13" s="0">
-        <v>5.5742869582935066</v>
+        <v>5.2900211313264016</v>
       </c>
       <c r="S13" s="0">
-        <v>5.325723459645622</v>
+        <v>5.0865436231102557</v>
       </c>
       <c r="T13" s="0">
-        <v>5.0695843537903809</v>
+        <v>4.8813229350954073</v>
       </c>
       <c r="U13" s="0">
-        <v>4.8194093642022944</v>
+        <v>4.6842602315843545</v>
       </c>
       <c r="V13" s="0">
-        <v>4.590087695479868</v>
+        <v>4.5069647698544797</v>
       </c>
       <c r="W13" s="0">
-        <v>4.4051742609061613</v>
+        <v>4.3700124881127946</v>
       </c>
       <c r="X13" s="0">
-        <v>4.2653722094830258</v>
+        <v>4.2714116496851657</v>
       </c>
       <c r="Y13" s="0">
-        <v>4.1626856460212922</v>
+        <v>4.2025120655459167</v>
       </c>
       <c r="Z13" s="0">
-        <v>4.0885819376663308</v>
+        <v>4.1551498394955395</v>
       </c>
       <c r="AA13" s="0">
-        <v>4.035781492978491</v>
+        <v>4.1229527344283321</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>5.7993548593401236</v>
+        <v>6.0255604383483581</v>
       </c>
       <c r="B14" s="0">
-        <v>6.3224378842620901</v>
+        <v>5.6210581029032545</v>
       </c>
       <c r="C14" s="0">
-        <v>6.5776484692637931</v>
+        <v>5.2434607810681069</v>
       </c>
       <c r="D14" s="0">
-        <v>5.0640192241538049</v>
+        <v>5.0288468426608635</v>
       </c>
       <c r="E14" s="0">
-        <v>4.9972234804941511</v>
+        <v>4.9678254906186146</v>
       </c>
       <c r="F14" s="0">
-        <v>4.9205079121903754</v>
+        <v>4.8834007922916465</v>
       </c>
       <c r="G14" s="0">
-        <v>4.8706492803499213</v>
+        <v>4.8314440871030193</v>
       </c>
       <c r="H14" s="0">
-        <v>5.1725532234726472</v>
+        <v>5.2069112833516265</v>
       </c>
       <c r="I14" s="0">
-        <v>5.7726478499706966</v>
+        <v>5.8936823441216832</v>
       </c>
       <c r="J14" s="0">
-        <v>6.230562389220129</v>
+        <v>6.3489591507253174</v>
       </c>
       <c r="K14" s="0">
-        <v>6.1814624299680903</v>
+        <v>6.2265493920243609</v>
       </c>
       <c r="L14" s="0">
-        <v>6.2054344228358875</v>
+        <v>6.2593089237741078</v>
       </c>
       <c r="M14" s="0">
-        <v>6.2322405892067794</v>
+        <v>6.295494213147526</v>
       </c>
       <c r="N14" s="0">
-        <v>6.2429585631400304</v>
+        <v>6.3107534327988262</v>
       </c>
       <c r="O14" s="0">
-        <v>6.1868699076097338</v>
+        <v>6.256993039348739</v>
       </c>
       <c r="P14" s="0">
-        <v>6.0635460552712077</v>
+        <v>6.1337060497084774</v>
       </c>
       <c r="Q14" s="0">
-        <v>5.8786931742458579</v>
+        <v>5.9540480417935724</v>
       </c>
       <c r="R14" s="0">
-        <v>5.6596010280526086</v>
+        <v>5.7371795741800371</v>
       </c>
       <c r="S14" s="0">
-        <v>5.4240484175806838</v>
+        <v>5.5020580471052556</v>
       </c>
       <c r="T14" s="0">
-        <v>5.1824065550692691</v>
+        <v>5.2645059471489608</v>
       </c>
       <c r="U14" s="0">
-        <v>4.9369963531606356</v>
+        <v>5.0361119733198025</v>
       </c>
       <c r="V14" s="0">
-        <v>4.7349574978831406</v>
+        <v>4.8208000075782911</v>
       </c>
       <c r="W14" s="0">
-        <v>4.5501603916170836</v>
+        <v>4.6511817321508477</v>
       </c>
       <c r="X14" s="0">
-        <v>4.4138840568503266</v>
+        <v>4.5377230162027127</v>
       </c>
       <c r="Y14" s="0">
-        <v>4.3298831474070338</v>
+        <v>4.457818737702504</v>
       </c>
       <c r="Z14" s="0">
-        <v>4.2735904318639664</v>
+        <v>4.4031800439155111</v>
       </c>
       <c r="AA14" s="0">
-        <v>4.2351232275395363</v>
+        <v>4.3675991386645379</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>5.8127505442002727</v>
+        <v>6.3459701660162464</v>
       </c>
       <c r="B15" s="0">
-        <v>6.3392547391784877</v>
+        <v>5.9165705033746949</v>
       </c>
       <c r="C15" s="0">
-        <v>6.5917079479173548</v>
+        <v>5.5163494122852672</v>
       </c>
       <c r="D15" s="0">
-        <v>5.1956602407528756</v>
+        <v>5.2841746591402865</v>
       </c>
       <c r="E15" s="0">
-        <v>5.1444170639299589</v>
+        <v>5.2095147652677305</v>
       </c>
       <c r="F15" s="0">
-        <v>5.0708546946197677</v>
+        <v>5.1126321085863315</v>
       </c>
       <c r="G15" s="0">
-        <v>5.0258593702801422</v>
+        <v>5.0567691173318199</v>
       </c>
       <c r="H15" s="0">
-        <v>5.3145699738519063</v>
+        <v>5.4344482801652987</v>
       </c>
       <c r="I15" s="0">
-        <v>5.9935835918551863</v>
+        <v>6.1411277851684538</v>
       </c>
       <c r="J15" s="0">
-        <v>6.5155305808313191</v>
+        <v>6.6249500747259011</v>
       </c>
       <c r="K15" s="0">
-        <v>6.5023256571086199</v>
+        <v>6.4909918375685738</v>
       </c>
       <c r="L15" s="0">
-        <v>6.5523309305108937</v>
+        <v>6.5191707183540766</v>
       </c>
       <c r="M15" s="0">
-        <v>6.5971513899219083</v>
+        <v>6.5539075697400255</v>
       </c>
       <c r="N15" s="0">
-        <v>6.6171465927387967</v>
+        <v>6.565374915726423</v>
       </c>
       <c r="O15" s="0">
-        <v>6.5597552385409239</v>
+        <v>6.505328100334161</v>
       </c>
       <c r="P15" s="0">
-        <v>6.4233055268998758</v>
+        <v>6.3712136131888686</v>
       </c>
       <c r="Q15" s="0">
-        <v>6.2240461518134786</v>
+        <v>6.174718153749577</v>
       </c>
       <c r="R15" s="0">
-        <v>5.9839037788111238</v>
+        <v>5.9419021199764899</v>
       </c>
       <c r="S15" s="0">
-        <v>5.7240556317568174</v>
+        <v>5.6940058377058422</v>
       </c>
       <c r="T15" s="0">
-        <v>5.4620140462808093</v>
+        <v>5.4434033655676357</v>
       </c>
       <c r="U15" s="0">
-        <v>5.2105515136094773</v>
+        <v>5.2023583719727915</v>
       </c>
       <c r="V15" s="0">
-        <v>4.9843234262770455</v>
+        <v>4.9850905948451922</v>
       </c>
       <c r="W15" s="0">
-        <v>4.8104101273784474</v>
+        <v>4.8168354672948182</v>
       </c>
       <c r="X15" s="0">
-        <v>4.6861483646600917</v>
+        <v>4.6950849681902263</v>
       </c>
       <c r="Y15" s="0">
-        <v>4.5994568709460841</v>
+        <v>4.6124974769917193</v>
       </c>
       <c r="Z15" s="0">
-        <v>4.5398571845523357</v>
+        <v>4.5560925292649257</v>
       </c>
       <c r="AA15" s="0">
-        <v>4.4994110734792256</v>
+        <v>4.5173761119849161</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>5.8258988187153147</v>
+        <v>5.5015521298241152</v>
       </c>
       <c r="B16" s="0">
-        <v>6.3557950039083169</v>
+        <v>5.120911363747882</v>
       </c>
       <c r="C16" s="0">
-        <v>6.6059332415109813</v>
+        <v>4.7675943510544787</v>
       </c>
       <c r="D16" s="0">
-        <v>4.8429759674198296</v>
+        <v>4.5662605147835809</v>
       </c>
       <c r="E16" s="0">
-        <v>4.7897035556538725</v>
+        <v>4.5075868683203471</v>
       </c>
       <c r="F16" s="0">
-        <v>4.7167236006779261</v>
+        <v>4.4309514886866639</v>
       </c>
       <c r="G16" s="0">
-        <v>4.674838450921543</v>
+        <v>4.3896133393880765</v>
       </c>
       <c r="H16" s="0">
-        <v>4.9956514726037495</v>
+        <v>4.7462238310620304</v>
       </c>
       <c r="I16" s="0">
-        <v>5.6009457119042123</v>
+        <v>5.3978678547071937</v>
       </c>
       <c r="J16" s="0">
-        <v>6.0530331248341414</v>
+        <v>5.8257326020226348</v>
       </c>
       <c r="K16" s="0">
-        <v>6.0310245014807631</v>
+        <v>5.7078783177400538</v>
       </c>
       <c r="L16" s="0">
-        <v>6.0777639652529718</v>
+        <v>5.741336626097441</v>
       </c>
       <c r="M16" s="0">
-        <v>6.1188758828547085</v>
+        <v>5.7764519903091864</v>
       </c>
       <c r="N16" s="0">
-        <v>6.1272255671339657</v>
+        <v>5.776557859715477</v>
       </c>
       <c r="O16" s="0">
-        <v>6.0445530379836407</v>
+        <v>5.689021095445101</v>
       </c>
       <c r="P16" s="0">
-        <v>5.8758729978717934</v>
+        <v>5.5261417427216797</v>
       </c>
       <c r="Q16" s="0">
-        <v>5.6318188152382698</v>
+        <v>5.3024125615181017</v>
       </c>
       <c r="R16" s="0">
-        <v>5.3360508214098053</v>
+        <v>5.039322014806892</v>
       </c>
       <c r="S16" s="0">
-        <v>5.0159880599296809</v>
+        <v>4.7578346772075868</v>
       </c>
       <c r="T16" s="0">
-        <v>4.6851655176964817</v>
+        <v>4.4751872957498255</v>
       </c>
       <c r="U16" s="0">
-        <v>4.3593568861087011</v>
+        <v>4.2038113219318341</v>
       </c>
       <c r="V16" s="0">
-        <v>4.0721229451689869</v>
+        <v>3.9672079901801127</v>
       </c>
       <c r="W16" s="0">
-        <v>3.8542907165296239</v>
+        <v>3.7925692431379279</v>
       </c>
       <c r="X16" s="0">
-        <v>3.6943240757202327</v>
+        <v>3.6641777037199388</v>
       </c>
       <c r="Y16" s="0">
-        <v>3.5682193217954397</v>
+        <v>3.5719126086581632</v>
       </c>
       <c r="Z16" s="0">
-        <v>3.4752477155387651</v>
+        <v>3.5057629378205664</v>
       </c>
       <c r="AA16" s="0">
-        <v>3.4066088229487637</v>
+        <v>3.4579546280925779</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>5.8392075415920575</v>
+        <v>6.0255604383483581</v>
       </c>
       <c r="B17" s="0">
-        <v>6.3724343508623651</v>
+        <v>5.6210581029032545</v>
       </c>
       <c r="C17" s="0">
-        <v>6.6205107922678952</v>
+        <v>5.2434607810681069</v>
       </c>
       <c r="D17" s="0">
-        <v>5.0640192241538049</v>
+        <v>5.0288468426608635</v>
       </c>
       <c r="E17" s="0">
-        <v>4.9972234804941511</v>
+        <v>4.9678254906186146</v>
       </c>
       <c r="F17" s="0">
-        <v>4.9205079121903754</v>
+        <v>4.8834007922916465</v>
       </c>
       <c r="G17" s="0">
-        <v>4.8706492803499213</v>
+        <v>4.8314440871030193</v>
       </c>
       <c r="H17" s="0">
-        <v>5.1725532234726472</v>
+        <v>5.2069112833516265</v>
       </c>
       <c r="I17" s="0">
-        <v>5.7726478499706966</v>
+        <v>5.8936823441216832</v>
       </c>
       <c r="J17" s="0">
-        <v>6.230562389220129</v>
+        <v>6.3489591507253174</v>
       </c>
       <c r="K17" s="0">
-        <v>6.1814624299680903</v>
+        <v>6.2265493920243609</v>
       </c>
       <c r="L17" s="0">
-        <v>6.2054344228358875</v>
+        <v>6.2593089237741078</v>
       </c>
       <c r="M17" s="0">
-        <v>6.2322405833316479</v>
+        <v>6.2954942076918812</v>
       </c>
       <c r="N17" s="0">
-        <v>6.2317856483536209</v>
+        <v>6.2969346501279579</v>
       </c>
       <c r="O17" s="0">
-        <v>6.1436842712714261</v>
+        <v>6.1994223158201143</v>
       </c>
       <c r="P17" s="0">
-        <v>5.9710291201473149</v>
+        <v>6.0143737812951352</v>
       </c>
       <c r="Q17" s="0">
-        <v>5.7244275584312403</v>
+        <v>5.7587224674581146</v>
       </c>
       <c r="R17" s="0">
-        <v>5.4430298132538653</v>
+        <v>5.4572167122170887</v>
       </c>
       <c r="S17" s="0">
-        <v>5.1074640164912006</v>
+        <v>5.1340026047341674</v>
       </c>
       <c r="T17" s="0">
-        <v>4.7822177822424576</v>
+        <v>4.8090350238385389</v>
       </c>
       <c r="U17" s="0">
-        <v>4.4768135152832134</v>
+        <v>4.4968174419338034</v>
       </c>
       <c r="V17" s="0">
-        <v>4.1926392153116829</v>
+        <v>4.223837629014839</v>
       </c>
       <c r="W17" s="0">
-        <v>3.9674193482994902</v>
+        <v>4.0206981491323948</v>
       </c>
       <c r="X17" s="0">
-        <v>3.8154327671318731</v>
+        <v>3.8697871061916498</v>
       </c>
       <c r="Y17" s="0">
-        <v>3.7036290375577314</v>
+        <v>3.7597766467775227</v>
       </c>
       <c r="Z17" s="0">
-        <v>3.6214087949041836</v>
+        <v>3.6825815545811351</v>
       </c>
       <c r="AA17" s="0">
-        <v>3.5619795515176729</v>
+        <v>3.6262968980917956</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>5.8528189040171537</v>
+        <v>6.3459701660162464</v>
       </c>
       <c r="B18" s="0">
-        <v>6.389323348387352</v>
+        <v>5.9165705033746949</v>
       </c>
       <c r="C18" s="0">
-        <v>6.6354810386307266</v>
+        <v>5.5163494122852672</v>
       </c>
       <c r="D18" s="0">
-        <v>5.1956602407528756</v>
+        <v>5.2841746591402865</v>
       </c>
       <c r="E18" s="0">
-        <v>5.1444170639299589</v>
+        <v>5.2095147652677305</v>
       </c>
       <c r="F18" s="0">
-        <v>5.0708546946197677</v>
+        <v>5.1126321085863315</v>
       </c>
       <c r="G18" s="0">
-        <v>5.0258593702801422</v>
+        <v>5.0567691173318199</v>
       </c>
       <c r="H18" s="0">
-        <v>5.3145699738519063</v>
+        <v>5.4344482801652987</v>
       </c>
       <c r="I18" s="0">
-        <v>5.9935835918551863</v>
+        <v>6.1411277851684538</v>
       </c>
       <c r="J18" s="0">
-        <v>6.5155305808313191</v>
+        <v>6.6249500747259011</v>
       </c>
       <c r="K18" s="0">
-        <v>6.5023256571086199</v>
+        <v>6.4909918375685738</v>
       </c>
       <c r="L18" s="0">
-        <v>6.5523309305108937</v>
+        <v>6.5191707183540766</v>
       </c>
       <c r="M18" s="0">
-        <v>6.5971513564903743</v>
+        <v>6.5539075856763001</v>
       </c>
       <c r="N18" s="0">
-        <v>6.6058660754374348</v>
+        <v>6.55095652697681</v>
       </c>
       <c r="O18" s="0">
-        <v>6.5102586461607119</v>
+        <v>6.4452633931624694</v>
       </c>
       <c r="P18" s="0">
-        <v>6.3143992448587323</v>
+        <v>6.2461162582855003</v>
       </c>
       <c r="Q18" s="0">
-        <v>6.0398043440775337</v>
+        <v>5.9720497418452201</v>
       </c>
       <c r="R18" s="0">
-        <v>5.7149180792527901</v>
+        <v>5.6609721065362422</v>
       </c>
       <c r="S18" s="0">
-        <v>5.36669065834145</v>
+        <v>5.3257511306255019</v>
       </c>
       <c r="T18" s="0">
-        <v>5.0171909963426575</v>
+        <v>4.9871768715287059</v>
       </c>
       <c r="U18" s="0">
-        <v>4.6823704853131538</v>
+        <v>4.6607885506314739</v>
       </c>
       <c r="V18" s="0">
-        <v>4.3875833653920173</v>
+        <v>4.3740592428619145</v>
       </c>
       <c r="W18" s="0">
-        <v>4.165027681719307</v>
+        <v>4.1674511789554103</v>
       </c>
       <c r="X18" s="0">
-        <v>4.0035735565280426</v>
+        <v>4.0191436977456325</v>
       </c>
       <c r="Y18" s="0">
-        <v>3.8880510789815808</v>
+        <v>3.9172050168502533</v>
       </c>
       <c r="Z18" s="0">
-        <v>3.8053900147493724</v>
+        <v>3.843822026844538</v>
       </c>
       <c r="AA18" s="0">
-        <v>3.7458933794414118</v>
+        <v>3.7904458319751409</v>
       </c>
     </row>
     <row r="19">
